--- a/analysis/dataview/multiple-tree-CoT.xlsx
+++ b/analysis/dataview/multiple-tree-CoT.xlsx
@@ -527,10 +527,10 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>17.845</v>
+        <v>20.04416666666667</v>
       </c>
       <c r="C2">
-        <v>19.55913202201328</v>
+        <v>19.05318892819082</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -541,10 +541,10 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>40.2875</v>
+        <v>59.24916666666667</v>
       </c>
       <c r="C3">
-        <v>8.348253083457315</v>
+        <v>9.516724473103638</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -555,10 +555,10 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>58.24</v>
+        <v>67.92999999999999</v>
       </c>
       <c r="C4">
-        <v>14.14464691548136</v>
+        <v>12.87218283388994</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -583,10 +583,10 @@
         <v>13</v>
       </c>
       <c r="B6">
-        <v>98.03166666666668</v>
+        <v>59.70333333333334</v>
       </c>
       <c r="C6">
-        <v>3.57607665499836</v>
+        <v>8.788410067535057</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -597,10 +597,10 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <v>97.66416666666667</v>
+        <v>77.65333333333334</v>
       </c>
       <c r="C7">
-        <v>3.764058395676212</v>
+        <v>10.54607840369916</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -625,10 +625,10 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>31.14416666666667</v>
+        <v>33.36416666666667</v>
       </c>
       <c r="C9">
-        <v>16.21272926288215</v>
+        <v>16.10450781519562</v>
       </c>
       <c r="D9">
         <v>12</v>
@@ -639,10 +639,10 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>89.59416666666668</v>
+        <v>62.385</v>
       </c>
       <c r="C10">
-        <v>12.77864515391585</v>
+        <v>25.68541591855368</v>
       </c>
       <c r="D10">
         <v>12</v>
@@ -677,10 +677,10 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>61.69972222222222</v>
+        <v>55.47222222222222</v>
       </c>
       <c r="C2">
-        <v>32.81605264728234</v>
+        <v>25.25970479536937</v>
       </c>
       <c r="D2">
         <v>36</v>
@@ -691,10 +691,10 @@
         <v>19</v>
       </c>
       <c r="B3">
-        <v>50.77222222222222</v>
+        <v>45.60277777777778</v>
       </c>
       <c r="C3">
-        <v>32.40146302791289</v>
+        <v>24.3510682207591</v>
       </c>
       <c r="D3">
         <v>36</v>
@@ -705,10 +705,10 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>56.63583333333334</v>
+        <v>50.54027777777778</v>
       </c>
       <c r="C4">
-        <v>33.49638977348369</v>
+        <v>24.46372865939767</v>
       </c>
       <c r="D4">
         <v>36</v>
@@ -743,10 +743,10 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>55.87314814814815</v>
+        <v>49.48388888888889</v>
       </c>
       <c r="C2">
-        <v>32.52892447711752</v>
+        <v>22.20763394299159</v>
       </c>
       <c r="D2">
         <v>54</v>
@@ -757,10 +757,10 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>56.86537037037037</v>
+        <v>51.59296296296296</v>
       </c>
       <c r="C3">
-        <v>33.57676918801928</v>
+        <v>27.3092912262772</v>
       </c>
       <c r="D3">
         <v>54</v>
@@ -795,10 +795,10 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>50.10055555555555</v>
+        <v>42.88555555555556</v>
       </c>
       <c r="C2">
-        <v>33.31205631467306</v>
+        <v>24.1698676951802</v>
       </c>
       <c r="D2">
         <v>54</v>
@@ -809,10 +809,10 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>62.63796296296296</v>
+        <v>58.19129629629629</v>
       </c>
       <c r="C3">
-        <v>31.56362806343567</v>
+        <v>23.18872668901253</v>
       </c>
       <c r="D3">
         <v>54</v>
